--- a/data/trans_orig/P16B13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,62 +880,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7517</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6810</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,97 +1188,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5593</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1843</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1531,97 +1531,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1740</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51345</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,62 +1909,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,97 +2217,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48298</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57273</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>108176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>39,09%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3823,97 +3823,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2212</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52454</t>
+          <t>52841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>60259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>84804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>93487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51559</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,62 +4887,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5195,97 +5195,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180410</t>
+          <t>180382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188194</t>
+          <t>188208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306103</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321819</t>
+          <t>320994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016 (tasa de respuesta: 97,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6458,97 +6458,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5032</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>973</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5580</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5105</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7144,97 +7144,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45590</t>
+          <t>44776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7487,97 +7487,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>1194</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7830,97 +7830,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2158</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83161</t>
+          <t>81524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94275</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215874</t>
+          <t>216449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>230559</t>
+          <t>230366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16B13-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Clase-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48147</t>
+          <t>48543</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55164</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50303</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57260</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>84579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200197</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35450</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52841</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60259</t>
+          <t>60323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84804</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93487</t>
+          <t>93485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68002</t>
+          <t>67828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180382</t>
+          <t>181348</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>305307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>320994</t>
+          <t>321749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44776</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81524</t>
+          <t>82503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94242</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216449</t>
+          <t>215614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>230366</t>
+          <t>230795</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
